--- a/data/Capstone_Dataset_Cleaned_ML.xlsx
+++ b/data/Capstone_Dataset_Cleaned_ML.xlsx
@@ -1,30 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Juliana\Downloads\palaysense-web222-20260722T041652Z-1-001\palaysense-web222\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F857FF3F-B2B5-42EB-97B2-9CE0BA923BC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bataan_Dataset" sheetId="1" r:id="rId1"/>
     <sheet name="Palay_Sufficiency_Bataan" sheetId="2" r:id="rId2"/>
     <sheet name="Palay_Production_per_Municipali" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="52">
   <si>
     <t>province</t>
   </si>
   <si>
     <t>year</t>
-  </si>
-  <si>
-    <t>month</t>
   </si>
   <si>
     <t>month_num</t>
@@ -167,15 +183,24 @@
   <si>
     <t>Bagac</t>
   </si>
+  <si>
+    <t>Province</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Month</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -187,6 +212,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -227,25 +258,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -283,7 +323,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -317,6 +357,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -351,9 +392,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -526,72 +568,75 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q133"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Q139"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="17" width="18.28515625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17">
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B2">
         <v>2015</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -627,7 +672,7 @@
         <v>26.76</v>
       </c>
       <c r="O2">
-        <v>19.24</v>
+        <v>19.239999999999998</v>
       </c>
       <c r="P2">
         <v>5.15</v>
@@ -636,15 +681,15 @@
         <v>42005</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B3">
         <v>2015</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -689,15 +734,15 @@
         <v>42036</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4">
         <v>2015</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -733,7 +778,7 @@
         <v>26.76</v>
       </c>
       <c r="O4">
-        <v>17.85</v>
+        <v>17.850000000000001</v>
       </c>
       <c r="P4">
         <v>5.15</v>
@@ -742,15 +787,15 @@
         <v>42064</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5">
         <v>2015</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -795,15 +840,15 @@
         <v>42095</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6">
         <v>2015</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -848,15 +893,15 @@
         <v>42125</v>
       </c>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7">
         <v>2015</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -892,7 +937,7 @@
         <v>26.76</v>
       </c>
       <c r="O7">
-        <v>17.67</v>
+        <v>17.670000000000002</v>
       </c>
       <c r="P7">
         <v>5.08</v>
@@ -901,15 +946,15 @@
         <v>42156</v>
       </c>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8">
         <v>2015</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -945,24 +990,24 @@
         <v>26.76</v>
       </c>
       <c r="O8">
-        <v>17.67</v>
+        <v>17.670000000000002</v>
       </c>
       <c r="P8">
-        <v>4.65</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="Q8" s="2">
         <v>42186</v>
       </c>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9">
         <v>2015</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -998,24 +1043,24 @@
         <v>26.76</v>
       </c>
       <c r="O9">
-        <v>17.67</v>
+        <v>17.670000000000002</v>
       </c>
       <c r="P9">
-        <v>4.65</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="Q9" s="2">
         <v>42217</v>
       </c>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10">
         <v>2015</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -1054,21 +1099,21 @@
         <v>17.88</v>
       </c>
       <c r="P10">
-        <v>4.65</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="Q10" s="2">
         <v>42248</v>
       </c>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11">
         <v>2015</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -1107,21 +1152,21 @@
         <v>18.18</v>
       </c>
       <c r="P11">
-        <v>4.27</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="Q11" s="2">
         <v>42278</v>
       </c>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B12">
         <v>2015</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D12">
         <v>11</v>
@@ -1160,21 +1205,21 @@
         <v>18.11</v>
       </c>
       <c r="P12">
-        <v>4.27</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="Q12" s="2">
         <v>42309</v>
       </c>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B13">
         <v>2015</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D13">
         <v>12</v>
@@ -1213,21 +1258,21 @@
         <v>18.14</v>
       </c>
       <c r="P13">
-        <v>4.27</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="Q13" s="2">
         <v>42339</v>
       </c>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14">
         <v>2016</v>
       </c>
       <c r="C14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -1272,15 +1317,15 @@
         <v>42370</v>
       </c>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B15">
         <v>2016</v>
       </c>
       <c r="C15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D15">
         <v>2</v>
@@ -1325,15 +1370,15 @@
         <v>42401</v>
       </c>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B16">
         <v>2016</v>
       </c>
       <c r="C16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D16">
         <v>3</v>
@@ -1378,15 +1423,15 @@
         <v>42430</v>
       </c>
     </row>
-    <row r="17" spans="1:17">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B17">
         <v>2016</v>
       </c>
       <c r="C17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D17">
         <v>4</v>
@@ -1422,24 +1467,24 @@
         <v>26.76</v>
       </c>
       <c r="O17">
-        <v>16.94</v>
+        <v>16.940000000000001</v>
       </c>
       <c r="P17">
-        <v>4.15</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="Q17" s="2">
         <v>42461</v>
       </c>
     </row>
-    <row r="18" spans="1:17">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18">
         <v>2016</v>
       </c>
       <c r="C18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D18">
         <v>5</v>
@@ -1478,21 +1523,21 @@
         <v>16.36</v>
       </c>
       <c r="P18">
-        <v>4.15</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="Q18" s="2">
         <v>42491</v>
       </c>
     </row>
-    <row r="19" spans="1:17">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B19">
         <v>2016</v>
       </c>
       <c r="C19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D19">
         <v>6</v>
@@ -1531,21 +1576,21 @@
         <v>17.72</v>
       </c>
       <c r="P19">
-        <v>4.15</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="Q19" s="2">
         <v>42522</v>
       </c>
     </row>
-    <row r="20" spans="1:17">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B20">
         <v>2016</v>
       </c>
       <c r="C20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D20">
         <v>7</v>
@@ -1581,24 +1626,24 @@
         <v>26.76</v>
       </c>
       <c r="O20">
-        <v>18.6</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="P20">
-        <v>4.23</v>
+        <v>4.2300000000000004</v>
       </c>
       <c r="Q20" s="2">
         <v>42552</v>
       </c>
     </row>
-    <row r="21" spans="1:17">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B21">
         <v>2016</v>
       </c>
       <c r="C21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D21">
         <v>8</v>
@@ -1634,24 +1679,24 @@
         <v>26.76</v>
       </c>
       <c r="O21">
-        <v>18.15</v>
+        <v>18.149999999999999</v>
       </c>
       <c r="P21">
-        <v>4.23</v>
+        <v>4.2300000000000004</v>
       </c>
       <c r="Q21" s="2">
         <v>42583</v>
       </c>
     </row>
-    <row r="22" spans="1:17">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B22">
         <v>2016</v>
       </c>
       <c r="C22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D22">
         <v>9</v>
@@ -1690,21 +1735,21 @@
         <v>19</v>
       </c>
       <c r="P22">
-        <v>4.23</v>
+        <v>4.2300000000000004</v>
       </c>
       <c r="Q22" s="2">
         <v>42614</v>
       </c>
     </row>
-    <row r="23" spans="1:17">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B23">
         <v>2016</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D23">
         <v>10</v>
@@ -1740,7 +1785,7 @@
         <v>26.76</v>
       </c>
       <c r="O23">
-        <v>17.94</v>
+        <v>17.940000000000001</v>
       </c>
       <c r="P23">
         <v>3.65</v>
@@ -1749,15 +1794,15 @@
         <v>42644</v>
       </c>
     </row>
-    <row r="24" spans="1:17">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B24">
         <v>2016</v>
       </c>
       <c r="C24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D24">
         <v>11</v>
@@ -1802,15 +1847,15 @@
         <v>42675</v>
       </c>
     </row>
-    <row r="25" spans="1:17">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B25">
         <v>2016</v>
       </c>
       <c r="C25" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D25">
         <v>12</v>
@@ -1855,15 +1900,15 @@
         <v>42705</v>
       </c>
     </row>
-    <row r="26" spans="1:17">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B26">
         <v>2017</v>
       </c>
       <c r="C26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -1902,21 +1947,21 @@
         <v>18</v>
       </c>
       <c r="P26">
-        <v>4.94</v>
+        <v>4.9400000000000004</v>
       </c>
       <c r="Q26" s="2">
         <v>42736</v>
       </c>
     </row>
-    <row r="27" spans="1:17">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B27">
         <v>2017</v>
       </c>
       <c r="C27" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D27">
         <v>2</v>
@@ -1955,21 +2000,21 @@
         <v>19.2</v>
       </c>
       <c r="P27">
-        <v>4.94</v>
+        <v>4.9400000000000004</v>
       </c>
       <c r="Q27" s="2">
         <v>42767</v>
       </c>
     </row>
-    <row r="28" spans="1:17">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B28">
         <v>2017</v>
       </c>
       <c r="C28" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D28">
         <v>3</v>
@@ -2008,21 +2053,21 @@
         <v>19.18</v>
       </c>
       <c r="P28">
-        <v>4.94</v>
+        <v>4.9400000000000004</v>
       </c>
       <c r="Q28" s="2">
         <v>42795</v>
       </c>
     </row>
-    <row r="29" spans="1:17">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B29">
         <v>2017</v>
       </c>
       <c r="C29" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D29">
         <v>4</v>
@@ -2061,21 +2106,21 @@
         <v>18.63</v>
       </c>
       <c r="P29">
-        <v>4.02</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="Q29" s="2">
         <v>42826</v>
       </c>
     </row>
-    <row r="30" spans="1:17">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B30">
         <v>2017</v>
       </c>
       <c r="C30" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D30">
         <v>5</v>
@@ -2114,21 +2159,21 @@
         <v>19</v>
       </c>
       <c r="P30">
-        <v>4.02</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="Q30" s="2">
         <v>42856</v>
       </c>
     </row>
-    <row r="31" spans="1:17">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B31">
         <v>2017</v>
       </c>
       <c r="C31" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D31">
         <v>6</v>
@@ -2167,21 +2212,21 @@
         <v>19</v>
       </c>
       <c r="P31">
-        <v>4.02</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="Q31" s="2">
         <v>42887</v>
       </c>
     </row>
-    <row r="32" spans="1:17">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B32">
         <v>2017</v>
       </c>
       <c r="C32" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D32">
         <v>7</v>
@@ -2226,15 +2271,15 @@
         <v>42917</v>
       </c>
     </row>
-    <row r="33" spans="1:17">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B33">
         <v>2017</v>
       </c>
       <c r="C33" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D33">
         <v>8</v>
@@ -2270,7 +2315,7 @@
         <v>26.76</v>
       </c>
       <c r="O33">
-        <v>18.83</v>
+        <v>18.829999999999998</v>
       </c>
       <c r="P33">
         <v>4.47</v>
@@ -2279,15 +2324,15 @@
         <v>42948</v>
       </c>
     </row>
-    <row r="34" spans="1:17">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B34">
         <v>2017</v>
       </c>
       <c r="C34" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D34">
         <v>9</v>
@@ -2323,7 +2368,7 @@
         <v>26.76</v>
       </c>
       <c r="O34">
-        <v>20.19</v>
+        <v>20.190000000000001</v>
       </c>
       <c r="P34">
         <v>4.47</v>
@@ -2332,15 +2377,15 @@
         <v>42979</v>
       </c>
     </row>
-    <row r="35" spans="1:17">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B35">
         <v>2017</v>
       </c>
       <c r="C35" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D35">
         <v>10</v>
@@ -2376,7 +2421,7 @@
         <v>26.76</v>
       </c>
       <c r="O35">
-        <v>19.26</v>
+        <v>19.260000000000002</v>
       </c>
       <c r="P35">
         <v>4.37</v>
@@ -2385,15 +2430,15 @@
         <v>43009</v>
       </c>
     </row>
-    <row r="36" spans="1:17">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B36">
         <v>2017</v>
       </c>
       <c r="C36" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D36">
         <v>11</v>
@@ -2438,15 +2483,15 @@
         <v>43040</v>
       </c>
     </row>
-    <row r="37" spans="1:17">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B37">
         <v>2017</v>
       </c>
       <c r="C37" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D37">
         <v>12</v>
@@ -2482,7 +2527,7 @@
         <v>26.76</v>
       </c>
       <c r="O37">
-        <v>18.33</v>
+        <v>18.329999999999998</v>
       </c>
       <c r="P37">
         <v>4.37</v>
@@ -2491,15 +2536,15 @@
         <v>43070</v>
       </c>
     </row>
-    <row r="38" spans="1:17">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B38">
         <v>2018</v>
       </c>
       <c r="C38" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D38">
         <v>1</v>
@@ -2517,7 +2562,7 @@
         <v>47999</v>
       </c>
       <c r="I38">
-        <v>130490.24</v>
+        <v>130490.24000000001</v>
       </c>
       <c r="J38">
         <v>10604</v>
@@ -2544,15 +2589,15 @@
         <v>43101</v>
       </c>
     </row>
-    <row r="39" spans="1:17">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B39">
         <v>2018</v>
       </c>
       <c r="C39" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D39">
         <v>2</v>
@@ -2570,7 +2615,7 @@
         <v>47999</v>
       </c>
       <c r="I39">
-        <v>130490.24</v>
+        <v>130490.24000000001</v>
       </c>
       <c r="J39">
         <v>10604</v>
@@ -2597,15 +2642,15 @@
         <v>43132</v>
       </c>
     </row>
-    <row r="40" spans="1:17">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B40">
         <v>2018</v>
       </c>
       <c r="C40" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D40">
         <v>3</v>
@@ -2623,7 +2668,7 @@
         <v>47999</v>
       </c>
       <c r="I40">
-        <v>130490.24</v>
+        <v>130490.24000000001</v>
       </c>
       <c r="J40">
         <v>10604</v>
@@ -2650,15 +2695,15 @@
         <v>43160</v>
       </c>
     </row>
-    <row r="41" spans="1:17">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B41">
         <v>2018</v>
       </c>
       <c r="C41" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D41">
         <v>4</v>
@@ -2676,7 +2721,7 @@
         <v>20744</v>
       </c>
       <c r="I41">
-        <v>130490.24</v>
+        <v>130490.24000000001</v>
       </c>
       <c r="J41">
         <v>4571</v>
@@ -2694,7 +2739,7 @@
         <v>26.76</v>
       </c>
       <c r="O41">
-        <v>17.6</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="P41">
         <v>4.54</v>
@@ -2703,15 +2748,15 @@
         <v>43191</v>
       </c>
     </row>
-    <row r="42" spans="1:17">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B42">
         <v>2018</v>
       </c>
       <c r="C42" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D42">
         <v>5</v>
@@ -2729,7 +2774,7 @@
         <v>20744</v>
       </c>
       <c r="I42">
-        <v>130490.24</v>
+        <v>130490.24000000001</v>
       </c>
       <c r="J42">
         <v>4571</v>
@@ -2756,15 +2801,15 @@
         <v>43221</v>
       </c>
     </row>
-    <row r="43" spans="1:17">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B43">
         <v>2018</v>
       </c>
       <c r="C43" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D43">
         <v>6</v>
@@ -2782,7 +2827,7 @@
         <v>20744</v>
       </c>
       <c r="I43">
-        <v>130490.24</v>
+        <v>130490.24000000001</v>
       </c>
       <c r="J43">
         <v>4571</v>
@@ -2809,15 +2854,15 @@
         <v>43252</v>
       </c>
     </row>
-    <row r="44" spans="1:17">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B44">
         <v>2018</v>
       </c>
       <c r="C44" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D44">
         <v>7</v>
@@ -2835,7 +2880,7 @@
         <v>13627.24</v>
       </c>
       <c r="I44">
-        <v>130490.24</v>
+        <v>130490.24000000001</v>
       </c>
       <c r="J44">
         <v>3536</v>
@@ -2862,15 +2907,15 @@
         <v>43282</v>
       </c>
     </row>
-    <row r="45" spans="1:17">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B45">
         <v>2018</v>
       </c>
       <c r="C45" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D45">
         <v>8</v>
@@ -2888,7 +2933,7 @@
         <v>13627.24</v>
       </c>
       <c r="I45">
-        <v>130490.24</v>
+        <v>130490.24000000001</v>
       </c>
       <c r="J45">
         <v>3536</v>
@@ -2915,15 +2960,15 @@
         <v>43313</v>
       </c>
     </row>
-    <row r="46" spans="1:17">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B46">
         <v>2018</v>
       </c>
       <c r="C46" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D46">
         <v>9</v>
@@ -2941,7 +2986,7 @@
         <v>13627.24</v>
       </c>
       <c r="I46">
-        <v>130490.24</v>
+        <v>130490.24000000001</v>
       </c>
       <c r="J46">
         <v>3536</v>
@@ -2968,15 +3013,15 @@
         <v>43344</v>
       </c>
     </row>
-    <row r="47" spans="1:17">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B47">
         <v>2018</v>
       </c>
       <c r="C47" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D47">
         <v>10</v>
@@ -2994,7 +3039,7 @@
         <v>48120</v>
       </c>
       <c r="I47">
-        <v>130490.24</v>
+        <v>130490.24000000001</v>
       </c>
       <c r="J47">
         <v>11301</v>
@@ -3015,21 +3060,21 @@
         <v>21.3</v>
       </c>
       <c r="P47">
-        <v>4.11</v>
+        <v>4.1100000000000003</v>
       </c>
       <c r="Q47" s="2">
         <v>43374</v>
       </c>
     </row>
-    <row r="48" spans="1:17">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B48">
         <v>2018</v>
       </c>
       <c r="C48" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D48">
         <v>11</v>
@@ -3047,7 +3092,7 @@
         <v>48120</v>
       </c>
       <c r="I48">
-        <v>130490.24</v>
+        <v>130490.24000000001</v>
       </c>
       <c r="J48">
         <v>11301</v>
@@ -3068,21 +3113,21 @@
         <v>21.7</v>
       </c>
       <c r="P48">
-        <v>4.11</v>
+        <v>4.1100000000000003</v>
       </c>
       <c r="Q48" s="2">
         <v>43405</v>
       </c>
     </row>
-    <row r="49" spans="1:17">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B49">
         <v>2018</v>
       </c>
       <c r="C49" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D49">
         <v>12</v>
@@ -3100,7 +3145,7 @@
         <v>48120</v>
       </c>
       <c r="I49">
-        <v>130490.24</v>
+        <v>130490.24000000001</v>
       </c>
       <c r="J49">
         <v>11301</v>
@@ -3121,21 +3166,21 @@
         <v>22.36</v>
       </c>
       <c r="P49">
-        <v>4.11</v>
+        <v>4.1100000000000003</v>
       </c>
       <c r="Q49" s="2">
         <v>43435</v>
       </c>
     </row>
-    <row r="50" spans="1:17">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B50">
         <v>2019</v>
       </c>
       <c r="C50" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D50">
         <v>1</v>
@@ -3174,21 +3219,21 @@
         <v>19.91</v>
       </c>
       <c r="P50">
-        <v>4.36</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="Q50" s="2">
         <v>43466</v>
       </c>
     </row>
-    <row r="51" spans="1:17">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B51">
         <v>2019</v>
       </c>
       <c r="C51" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D51">
         <v>2</v>
@@ -3227,21 +3272,21 @@
         <v>21.61</v>
       </c>
       <c r="P51">
-        <v>4.36</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="Q51" s="2">
         <v>43497</v>
       </c>
     </row>
-    <row r="52" spans="1:17">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B52">
         <v>2019</v>
       </c>
       <c r="C52" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D52">
         <v>3</v>
@@ -3280,21 +3325,21 @@
         <v>21.79</v>
       </c>
       <c r="P52">
-        <v>4.36</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="Q52" s="2">
         <v>43525</v>
       </c>
     </row>
-    <row r="53" spans="1:17">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B53">
         <v>2019</v>
       </c>
       <c r="C53" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D53">
         <v>4</v>
@@ -3330,7 +3375,7 @@
         <v>26.68</v>
       </c>
       <c r="O53">
-        <v>18.33</v>
+        <v>18.329999999999998</v>
       </c>
       <c r="P53">
         <v>4.2</v>
@@ -3339,15 +3384,15 @@
         <v>43556</v>
       </c>
     </row>
-    <row r="54" spans="1:17">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B54">
         <v>2019</v>
       </c>
       <c r="C54" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D54">
         <v>5</v>
@@ -3392,15 +3437,15 @@
         <v>43586</v>
       </c>
     </row>
-    <row r="55" spans="1:17">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B55">
         <v>2019</v>
       </c>
       <c r="C55" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D55">
         <v>6</v>
@@ -3436,7 +3481,7 @@
         <v>23.67</v>
       </c>
       <c r="O55">
-        <v>18.65</v>
+        <v>18.649999999999999</v>
       </c>
       <c r="P55">
         <v>4.2</v>
@@ -3445,15 +3490,15 @@
         <v>43617</v>
       </c>
     </row>
-    <row r="56" spans="1:17">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B56">
         <v>2019</v>
       </c>
       <c r="C56" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D56">
         <v>7</v>
@@ -3492,21 +3537,21 @@
         <v>17.22</v>
       </c>
       <c r="P56">
-        <v>4.36</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="Q56" s="2">
         <v>43647</v>
       </c>
     </row>
-    <row r="57" spans="1:17">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B57">
         <v>2019</v>
       </c>
       <c r="C57" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D57">
         <v>8</v>
@@ -3545,21 +3590,21 @@
         <v>16.52</v>
       </c>
       <c r="P57">
-        <v>4.36</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="Q57" s="2">
         <v>43678</v>
       </c>
     </row>
-    <row r="58" spans="1:17">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B58">
         <v>2019</v>
       </c>
       <c r="C58" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D58">
         <v>9</v>
@@ -3592,27 +3637,27 @@
         <v>28478.45</v>
       </c>
       <c r="N58">
-        <v>19.69</v>
+        <v>19.690000000000001</v>
       </c>
       <c r="O58">
         <v>15.74</v>
       </c>
       <c r="P58">
-        <v>4.36</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="Q58" s="2">
         <v>43709</v>
       </c>
     </row>
-    <row r="59" spans="1:17">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B59">
         <v>2019</v>
       </c>
       <c r="C59" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D59">
         <v>10</v>
@@ -3657,15 +3702,15 @@
         <v>43739</v>
       </c>
     </row>
-    <row r="60" spans="1:17">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B60">
         <v>2019</v>
       </c>
       <c r="C60" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D60">
         <v>11</v>
@@ -3698,7 +3743,7 @@
         <v>28478.45</v>
       </c>
       <c r="N60">
-        <v>18.56</v>
+        <v>18.559999999999999</v>
       </c>
       <c r="O60">
         <v>14.89</v>
@@ -3710,15 +3755,15 @@
         <v>43770</v>
       </c>
     </row>
-    <row r="61" spans="1:17">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B61">
         <v>2019</v>
       </c>
       <c r="C61" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D61">
         <v>12</v>
@@ -3763,15 +3808,15 @@
         <v>43800</v>
       </c>
     </row>
-    <row r="62" spans="1:17">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B62">
         <v>2020</v>
       </c>
       <c r="C62" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D62">
         <v>1</v>
@@ -3804,7 +3849,7 @@
         <v>28264.07</v>
       </c>
       <c r="N62">
-        <v>17.69</v>
+        <v>17.690000000000001</v>
       </c>
       <c r="O62">
         <v>14.74</v>
@@ -3816,15 +3861,15 @@
         <v>43831</v>
       </c>
     </row>
-    <row r="63" spans="1:17">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B63">
         <v>2020</v>
       </c>
       <c r="C63" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D63">
         <v>2</v>
@@ -3869,15 +3914,15 @@
         <v>43862</v>
       </c>
     </row>
-    <row r="64" spans="1:17">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B64">
         <v>2020</v>
       </c>
       <c r="C64" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D64">
         <v>3</v>
@@ -3922,15 +3967,15 @@
         <v>43891</v>
       </c>
     </row>
-    <row r="65" spans="1:17">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B65">
         <v>2020</v>
       </c>
       <c r="C65" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D65">
         <v>4</v>
@@ -3969,21 +4014,21 @@
         <v>15.13</v>
       </c>
       <c r="P65">
-        <v>4.77</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="Q65" s="2">
         <v>43922</v>
       </c>
     </row>
-    <row r="66" spans="1:17">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B66">
         <v>2020</v>
       </c>
       <c r="C66" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D66">
         <v>5</v>
@@ -4016,27 +4061,27 @@
         <v>28264.07</v>
       </c>
       <c r="N66">
-        <v>18.92</v>
+        <v>18.920000000000002</v>
       </c>
       <c r="O66">
-        <v>16.01</v>
+        <v>16.010000000000002</v>
       </c>
       <c r="P66">
-        <v>4.77</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="Q66" s="2">
         <v>43952</v>
       </c>
     </row>
-    <row r="67" spans="1:17">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B67">
         <v>2020</v>
       </c>
       <c r="C67" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D67">
         <v>6</v>
@@ -4075,21 +4120,21 @@
         <v>17</v>
       </c>
       <c r="P67">
-        <v>4.77</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="Q67" s="2">
         <v>43983</v>
       </c>
     </row>
-    <row r="68" spans="1:17">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B68">
         <v>2020</v>
       </c>
       <c r="C68" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D68">
         <v>7</v>
@@ -4110,19 +4155,19 @@
         <v>125143</v>
       </c>
       <c r="J68">
-        <v>2284.07</v>
+        <v>2284.0700000000002</v>
       </c>
       <c r="K68">
         <v>0</v>
       </c>
       <c r="L68">
-        <v>2284.07</v>
+        <v>2284.0700000000002</v>
       </c>
       <c r="M68">
         <v>28264.07</v>
       </c>
       <c r="N68">
-        <v>20.33</v>
+        <v>20.329999999999998</v>
       </c>
       <c r="O68">
         <v>17.86</v>
@@ -4134,15 +4179,15 @@
         <v>44013</v>
       </c>
     </row>
-    <row r="69" spans="1:17">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B69">
         <v>2020</v>
       </c>
       <c r="C69" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D69">
         <v>8</v>
@@ -4163,13 +4208,13 @@
         <v>125143</v>
       </c>
       <c r="J69">
-        <v>2284.07</v>
+        <v>2284.0700000000002</v>
       </c>
       <c r="K69">
         <v>0</v>
       </c>
       <c r="L69">
-        <v>2284.07</v>
+        <v>2284.0700000000002</v>
       </c>
       <c r="M69">
         <v>28264.07</v>
@@ -4187,15 +4232,15 @@
         <v>44044</v>
       </c>
     </row>
-    <row r="70" spans="1:17">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B70">
         <v>2020</v>
       </c>
       <c r="C70" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D70">
         <v>9</v>
@@ -4216,13 +4261,13 @@
         <v>125143</v>
       </c>
       <c r="J70">
-        <v>2284.07</v>
+        <v>2284.0700000000002</v>
       </c>
       <c r="K70">
         <v>0</v>
       </c>
       <c r="L70">
-        <v>2284.07</v>
+        <v>2284.0700000000002</v>
       </c>
       <c r="M70">
         <v>28264.07</v>
@@ -4240,15 +4285,15 @@
         <v>44075</v>
       </c>
     </row>
-    <row r="71" spans="1:17">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B71">
         <v>2020</v>
       </c>
       <c r="C71" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D71">
         <v>10</v>
@@ -4293,15 +4338,15 @@
         <v>44105</v>
       </c>
     </row>
-    <row r="72" spans="1:17">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B72">
         <v>2020</v>
       </c>
       <c r="C72" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D72">
         <v>11</v>
@@ -4334,7 +4379,7 @@
         <v>28264.07</v>
       </c>
       <c r="N72">
-        <v>20.1</v>
+        <v>20.100000000000001</v>
       </c>
       <c r="O72">
         <v>17.71</v>
@@ -4346,15 +4391,15 @@
         <v>44136</v>
       </c>
     </row>
-    <row r="73" spans="1:17">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B73">
         <v>2020</v>
       </c>
       <c r="C73" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D73">
         <v>12</v>
@@ -4399,15 +4444,15 @@
         <v>44166</v>
       </c>
     </row>
-    <row r="74" spans="1:17">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B74">
         <v>2021</v>
       </c>
       <c r="C74" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D74">
         <v>1</v>
@@ -4428,13 +4473,13 @@
         <v>117143.05</v>
       </c>
       <c r="J74">
-        <v>8983.450000000001</v>
+        <v>8983.4500000000007</v>
       </c>
       <c r="K74">
         <v>0</v>
       </c>
       <c r="L74">
-        <v>8983.450000000001</v>
+        <v>8983.4500000000007</v>
       </c>
       <c r="M74">
         <v>26962.97</v>
@@ -4452,15 +4497,15 @@
         <v>44197</v>
       </c>
     </row>
-    <row r="75" spans="1:17">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B75">
         <v>2021</v>
       </c>
       <c r="C75" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D75">
         <v>2</v>
@@ -4481,13 +4526,13 @@
         <v>117143.05</v>
       </c>
       <c r="J75">
-        <v>8983.450000000001</v>
+        <v>8983.4500000000007</v>
       </c>
       <c r="K75">
         <v>0</v>
       </c>
       <c r="L75">
-        <v>8983.450000000001</v>
+        <v>8983.4500000000007</v>
       </c>
       <c r="M75">
         <v>26962.97</v>
@@ -4505,15 +4550,15 @@
         <v>44228</v>
       </c>
     </row>
-    <row r="76" spans="1:17">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B76">
         <v>2021</v>
       </c>
       <c r="C76" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D76">
         <v>3</v>
@@ -4534,13 +4579,13 @@
         <v>117143.05</v>
       </c>
       <c r="J76">
-        <v>8983.450000000001</v>
+        <v>8983.4500000000007</v>
       </c>
       <c r="K76">
         <v>0</v>
       </c>
       <c r="L76">
-        <v>8983.450000000001</v>
+        <v>8983.4500000000007</v>
       </c>
       <c r="M76">
         <v>26962.97</v>
@@ -4558,15 +4603,15 @@
         <v>44256</v>
       </c>
     </row>
-    <row r="77" spans="1:17">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B77">
         <v>2021</v>
       </c>
       <c r="C77" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D77">
         <v>4</v>
@@ -4605,21 +4650,21 @@
         <v>17.57</v>
       </c>
       <c r="P77">
-        <v>4.56</v>
+        <v>4.5599999999999996</v>
       </c>
       <c r="Q77" s="2">
         <v>44287</v>
       </c>
     </row>
-    <row r="78" spans="1:17">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B78">
         <v>2021</v>
       </c>
       <c r="C78" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D78">
         <v>5</v>
@@ -4658,21 +4703,21 @@
         <v>18</v>
       </c>
       <c r="P78">
-        <v>4.56</v>
+        <v>4.5599999999999996</v>
       </c>
       <c r="Q78" s="2">
         <v>44317</v>
       </c>
     </row>
-    <row r="79" spans="1:17">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B79">
         <v>2021</v>
       </c>
       <c r="C79" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D79">
         <v>6</v>
@@ -4705,27 +4750,27 @@
         <v>26962.97</v>
       </c>
       <c r="N79">
-        <v>22.135</v>
+        <v>22.135000000000002</v>
       </c>
       <c r="O79">
-        <v>16.06</v>
+        <v>16.059999999999999</v>
       </c>
       <c r="P79">
-        <v>4.56</v>
+        <v>4.5599999999999996</v>
       </c>
       <c r="Q79" s="2">
         <v>44348</v>
       </c>
     </row>
-    <row r="80" spans="1:17">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B80">
         <v>2021</v>
       </c>
       <c r="C80" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D80">
         <v>7</v>
@@ -4761,7 +4806,7 @@
         <v>19.27</v>
       </c>
       <c r="O80">
-        <v>16.06</v>
+        <v>16.059999999999999</v>
       </c>
       <c r="P80">
         <v>4.24</v>
@@ -4770,15 +4815,15 @@
         <v>44378</v>
       </c>
     </row>
-    <row r="81" spans="1:17">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B81">
         <v>2021</v>
       </c>
       <c r="C81" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D81">
         <v>8</v>
@@ -4811,7 +4856,7 @@
         <v>26962.97</v>
       </c>
       <c r="N81">
-        <v>18.925</v>
+        <v>18.925000000000001</v>
       </c>
       <c r="O81">
         <v>15.525</v>
@@ -4823,15 +4868,15 @@
         <v>44409</v>
       </c>
     </row>
-    <row r="82" spans="1:17">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B82">
         <v>2021</v>
       </c>
       <c r="C82" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D82">
         <v>9</v>
@@ -4864,7 +4909,7 @@
         <v>26962.97</v>
       </c>
       <c r="N82">
-        <v>18.58</v>
+        <v>18.579999999999998</v>
       </c>
       <c r="O82">
         <v>14.99</v>
@@ -4876,15 +4921,15 @@
         <v>44440</v>
       </c>
     </row>
-    <row r="83" spans="1:17">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B83">
         <v>2021</v>
       </c>
       <c r="C83" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D83">
         <v>10</v>
@@ -4929,15 +4974,15 @@
         <v>44470</v>
       </c>
     </row>
-    <row r="84" spans="1:17">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B84">
         <v>2021</v>
       </c>
       <c r="C84" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D84">
         <v>11</v>
@@ -4982,15 +5027,15 @@
         <v>44501</v>
       </c>
     </row>
-    <row r="85" spans="1:17">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B85">
         <v>2021</v>
       </c>
       <c r="C85" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D85">
         <v>12</v>
@@ -5035,15 +5080,15 @@
         <v>44531</v>
       </c>
     </row>
-    <row r="86" spans="1:17">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B86">
         <v>2022</v>
       </c>
       <c r="C86" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D86">
         <v>1</v>
@@ -5088,15 +5133,15 @@
         <v>44562</v>
       </c>
     </row>
-    <row r="87" spans="1:17">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B87">
         <v>2022</v>
       </c>
       <c r="C87" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D87">
         <v>2</v>
@@ -5129,10 +5174,10 @@
         <v>27034.69</v>
       </c>
       <c r="N87">
-        <v>19.81</v>
+        <v>19.809999999999999</v>
       </c>
       <c r="O87">
-        <v>17.67</v>
+        <v>17.670000000000002</v>
       </c>
       <c r="P87">
         <v>4.67</v>
@@ -5141,15 +5186,15 @@
         <v>44593</v>
       </c>
     </row>
-    <row r="88" spans="1:17">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B88">
         <v>2022</v>
       </c>
       <c r="C88" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D88">
         <v>3</v>
@@ -5185,7 +5230,7 @@
         <v>20.54</v>
       </c>
       <c r="O88">
-        <v>17.92</v>
+        <v>17.920000000000002</v>
       </c>
       <c r="P88">
         <v>4.67</v>
@@ -5194,15 +5239,15 @@
         <v>44621</v>
       </c>
     </row>
-    <row r="89" spans="1:17">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B89">
         <v>2022</v>
       </c>
       <c r="C89" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D89">
         <v>4</v>
@@ -5235,10 +5280,10 @@
         <v>27034.69</v>
       </c>
       <c r="N89">
-        <v>19.69</v>
+        <v>19.690000000000001</v>
       </c>
       <c r="O89">
-        <v>17.01</v>
+        <v>17.010000000000002</v>
       </c>
       <c r="P89">
         <v>4.49</v>
@@ -5247,15 +5292,15 @@
         <v>44652</v>
       </c>
     </row>
-    <row r="90" spans="1:17">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B90">
         <v>2022</v>
       </c>
       <c r="C90" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D90">
         <v>5</v>
@@ -5288,10 +5333,10 @@
         <v>27034.69</v>
       </c>
       <c r="N90">
-        <v>16.83</v>
+        <v>16.829999999999998</v>
       </c>
       <c r="O90">
-        <v>17.24</v>
+        <v>17.239999999999998</v>
       </c>
       <c r="P90">
         <v>4.49</v>
@@ -5300,15 +5345,15 @@
         <v>44682</v>
       </c>
     </row>
-    <row r="91" spans="1:17">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B91">
         <v>2022</v>
       </c>
       <c r="C91" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D91">
         <v>6</v>
@@ -5353,15 +5398,15 @@
         <v>44713</v>
       </c>
     </row>
-    <row r="92" spans="1:17">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B92">
         <v>2022</v>
       </c>
       <c r="C92" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D92">
         <v>7</v>
@@ -5397,7 +5442,7 @@
         <v>18.2</v>
       </c>
       <c r="O92">
-        <v>16.06</v>
+        <v>16.059999999999999</v>
       </c>
       <c r="P92">
         <v>4.3</v>
@@ -5406,15 +5451,15 @@
         <v>44743</v>
       </c>
     </row>
-    <row r="93" spans="1:17">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B93">
         <v>2022</v>
       </c>
       <c r="C93" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D93">
         <v>8</v>
@@ -5459,15 +5504,15 @@
         <v>44774</v>
       </c>
     </row>
-    <row r="94" spans="1:17">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B94">
         <v>2022</v>
       </c>
       <c r="C94" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D94">
         <v>9</v>
@@ -5500,7 +5545,7 @@
         <v>27034.69</v>
       </c>
       <c r="N94">
-        <v>16.94</v>
+        <v>16.940000000000001</v>
       </c>
       <c r="O94">
         <v>14.81</v>
@@ -5512,15 +5557,15 @@
         <v>44805</v>
       </c>
     </row>
-    <row r="95" spans="1:17">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B95">
         <v>2022</v>
       </c>
       <c r="C95" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D95">
         <v>10</v>
@@ -5541,7 +5586,7 @@
         <v>115402.46</v>
       </c>
       <c r="J95">
-        <v>10335.3</v>
+        <v>10335.299999999999</v>
       </c>
       <c r="K95">
         <v>319</v>
@@ -5556,7 +5601,7 @@
         <v>19.53</v>
       </c>
       <c r="O95">
-        <v>17.15</v>
+        <v>17.149999999999999</v>
       </c>
       <c r="P95">
         <v>3.79</v>
@@ -5565,15 +5610,15 @@
         <v>44835</v>
       </c>
     </row>
-    <row r="96" spans="1:17">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B96">
         <v>2022</v>
       </c>
       <c r="C96" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D96">
         <v>11</v>
@@ -5594,7 +5639,7 @@
         <v>115402.46</v>
       </c>
       <c r="J96">
-        <v>10335.3</v>
+        <v>10335.299999999999</v>
       </c>
       <c r="K96">
         <v>319</v>
@@ -5618,15 +5663,15 @@
         <v>44866</v>
       </c>
     </row>
-    <row r="97" spans="1:17">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B97">
         <v>2022</v>
       </c>
       <c r="C97" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D97">
         <v>12</v>
@@ -5647,7 +5692,7 @@
         <v>115402.46</v>
       </c>
       <c r="J97">
-        <v>10335.3</v>
+        <v>10335.299999999999</v>
       </c>
       <c r="K97">
         <v>319</v>
@@ -5671,15 +5716,15 @@
         <v>44896</v>
       </c>
     </row>
-    <row r="98" spans="1:17">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B98">
         <v>2023</v>
       </c>
       <c r="C98" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -5688,13 +5733,13 @@
         <v>1</v>
       </c>
       <c r="F98">
-        <v>41789.84</v>
+        <v>41789.839999999997</v>
       </c>
       <c r="G98">
         <v>0</v>
       </c>
       <c r="H98">
-        <v>41789.84</v>
+        <v>41789.839999999997</v>
       </c>
       <c r="I98">
         <v>109195.3</v>
@@ -5724,15 +5769,15 @@
         <v>44927</v>
       </c>
     </row>
-    <row r="99" spans="1:17">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B99">
         <v>2023</v>
       </c>
       <c r="C99" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -5741,13 +5786,13 @@
         <v>1</v>
       </c>
       <c r="F99">
-        <v>41789.84</v>
+        <v>41789.839999999997</v>
       </c>
       <c r="G99">
         <v>0</v>
       </c>
       <c r="H99">
-        <v>41789.84</v>
+        <v>41789.839999999997</v>
       </c>
       <c r="I99">
         <v>109195.3</v>
@@ -5765,7 +5810,7 @@
         <v>25979.63</v>
       </c>
       <c r="N99">
-        <v>20.19</v>
+        <v>20.190000000000001</v>
       </c>
       <c r="O99">
         <v>19.03</v>
@@ -5777,15 +5822,15 @@
         <v>44958</v>
       </c>
     </row>
-    <row r="100" spans="1:17">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B100">
         <v>2023</v>
       </c>
       <c r="C100" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -5794,13 +5839,13 @@
         <v>1</v>
       </c>
       <c r="F100">
-        <v>41789.84</v>
+        <v>41789.839999999997</v>
       </c>
       <c r="G100">
         <v>0</v>
       </c>
       <c r="H100">
-        <v>41789.84</v>
+        <v>41789.839999999997</v>
       </c>
       <c r="I100">
         <v>109195.3</v>
@@ -5830,15 +5875,15 @@
         <v>44986</v>
       </c>
     </row>
-    <row r="101" spans="1:17">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B101">
         <v>2023</v>
       </c>
       <c r="C101" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D101">
         <v>4</v>
@@ -5883,15 +5928,15 @@
         <v>45017</v>
       </c>
     </row>
-    <row r="102" spans="1:17">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B102">
         <v>2023</v>
       </c>
       <c r="C102" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D102">
         <v>5</v>
@@ -5927,7 +5972,7 @@
         <v>21.74</v>
       </c>
       <c r="O102">
-        <v>19.15</v>
+        <v>19.149999999999999</v>
       </c>
       <c r="P102">
         <v>4.12</v>
@@ -5936,15 +5981,15 @@
         <v>45047</v>
       </c>
     </row>
-    <row r="103" spans="1:17">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B103">
         <v>2023</v>
       </c>
       <c r="C103" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D103">
         <v>6</v>
@@ -5989,15 +6034,15 @@
         <v>45078</v>
       </c>
     </row>
-    <row r="104" spans="1:17">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B104">
         <v>2023</v>
       </c>
       <c r="C104" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D104">
         <v>7</v>
@@ -6018,19 +6063,19 @@
         <v>109195.3</v>
       </c>
       <c r="J104">
-        <v>518.3099999999999</v>
+        <v>518.30999999999995</v>
       </c>
       <c r="K104">
         <v>0</v>
       </c>
       <c r="L104">
-        <v>518.3099999999999</v>
+        <v>518.30999999999995</v>
       </c>
       <c r="M104">
         <v>25979.63</v>
       </c>
       <c r="N104">
-        <v>22.82666666666666</v>
+        <v>22.826666666666661</v>
       </c>
       <c r="O104">
         <v>20.48</v>
@@ -6042,15 +6087,15 @@
         <v>45108</v>
       </c>
     </row>
-    <row r="105" spans="1:17">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B105">
         <v>2023</v>
       </c>
       <c r="C105" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D105">
         <v>8</v>
@@ -6071,13 +6116,13 @@
         <v>109195.3</v>
       </c>
       <c r="J105">
-        <v>518.3099999999999</v>
+        <v>518.30999999999995</v>
       </c>
       <c r="K105">
         <v>0</v>
       </c>
       <c r="L105">
-        <v>518.3099999999999</v>
+        <v>518.30999999999995</v>
       </c>
       <c r="M105">
         <v>25979.63</v>
@@ -6095,15 +6140,15 @@
         <v>45139</v>
       </c>
     </row>
-    <row r="106" spans="1:17">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B106">
         <v>2023</v>
       </c>
       <c r="C106" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D106">
         <v>9</v>
@@ -6124,13 +6169,13 @@
         <v>109195.3</v>
       </c>
       <c r="J106">
-        <v>518.3099999999999</v>
+        <v>518.30999999999995</v>
       </c>
       <c r="K106">
         <v>0</v>
       </c>
       <c r="L106">
-        <v>518.3099999999999</v>
+        <v>518.30999999999995</v>
       </c>
       <c r="M106">
         <v>25979.63</v>
@@ -6139,7 +6184,7 @@
         <v>21</v>
       </c>
       <c r="O106">
-        <v>17.6</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="P106">
         <v>4.08</v>
@@ -6148,15 +6193,15 @@
         <v>45170</v>
       </c>
     </row>
-    <row r="107" spans="1:17">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B107">
         <v>2023</v>
       </c>
       <c r="C107" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D107">
         <v>10</v>
@@ -6171,7 +6216,7 @@
         <v>1011.23</v>
       </c>
       <c r="H107">
-        <v>38959.41</v>
+        <v>38959.410000000003</v>
       </c>
       <c r="I107">
         <v>109195.3</v>
@@ -6201,15 +6246,15 @@
         <v>45200</v>
       </c>
     </row>
-    <row r="108" spans="1:17">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B108">
         <v>2023</v>
       </c>
       <c r="C108" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D108">
         <v>11</v>
@@ -6224,7 +6269,7 @@
         <v>1011.23</v>
       </c>
       <c r="H108">
-        <v>38959.41</v>
+        <v>38959.410000000003</v>
       </c>
       <c r="I108">
         <v>109195.3</v>
@@ -6254,15 +6299,15 @@
         <v>45231</v>
       </c>
     </row>
-    <row r="109" spans="1:17">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B109">
         <v>2023</v>
       </c>
       <c r="C109" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D109">
         <v>12</v>
@@ -6277,7 +6322,7 @@
         <v>1011.23</v>
       </c>
       <c r="H109">
-        <v>38959.41</v>
+        <v>38959.410000000003</v>
       </c>
       <c r="I109">
         <v>109195.3</v>
@@ -6307,15 +6352,15 @@
         <v>45261</v>
       </c>
     </row>
-    <row r="110" spans="1:17">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B110">
         <v>2024</v>
       </c>
       <c r="C110" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D110">
         <v>1</v>
@@ -6336,13 +6381,13 @@
         <v>107111.35</v>
       </c>
       <c r="J110">
-        <v>8985.530000000001</v>
+        <v>8985.5300000000007</v>
       </c>
       <c r="K110">
         <v>0</v>
       </c>
       <c r="L110">
-        <v>8985.530000000001</v>
+        <v>8985.5300000000007</v>
       </c>
       <c r="M110">
         <v>25366.06</v>
@@ -6354,21 +6399,21 @@
         <v>20.02</v>
       </c>
       <c r="P110">
-        <v>4.85</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="Q110" s="2">
         <v>45292</v>
       </c>
     </row>
-    <row r="111" spans="1:17">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B111">
         <v>2024</v>
       </c>
       <c r="C111" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D111">
         <v>2</v>
@@ -6389,13 +6434,13 @@
         <v>107111.35</v>
       </c>
       <c r="J111">
-        <v>8985.530000000001</v>
+        <v>8985.5300000000007</v>
       </c>
       <c r="K111">
         <v>0</v>
       </c>
       <c r="L111">
-        <v>8985.530000000001</v>
+        <v>8985.5300000000007</v>
       </c>
       <c r="M111">
         <v>25366.06</v>
@@ -6407,21 +6452,21 @@
         <v>26.3</v>
       </c>
       <c r="P111">
-        <v>4.85</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="Q111" s="2">
         <v>45323</v>
       </c>
     </row>
-    <row r="112" spans="1:17">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B112">
         <v>2024</v>
       </c>
       <c r="C112" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D112">
         <v>3</v>
@@ -6442,13 +6487,13 @@
         <v>107111.35</v>
       </c>
       <c r="J112">
-        <v>8985.530000000001</v>
+        <v>8985.5300000000007</v>
       </c>
       <c r="K112">
         <v>0</v>
       </c>
       <c r="L112">
-        <v>8985.530000000001</v>
+        <v>8985.5300000000007</v>
       </c>
       <c r="M112">
         <v>25366.06</v>
@@ -6460,21 +6505,21 @@
         <v>24.7</v>
       </c>
       <c r="P112">
-        <v>4.85</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="Q112" s="2">
         <v>45352</v>
       </c>
     </row>
-    <row r="113" spans="1:17">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B113">
         <v>2024</v>
       </c>
       <c r="C113" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D113">
         <v>4</v>
@@ -6519,15 +6564,15 @@
         <v>45383</v>
       </c>
     </row>
-    <row r="114" spans="1:17">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B114">
         <v>2024</v>
       </c>
       <c r="C114" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D114">
         <v>5</v>
@@ -6572,15 +6617,15 @@
         <v>45413</v>
       </c>
     </row>
-    <row r="115" spans="1:17">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B115">
         <v>2024</v>
       </c>
       <c r="C115" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D115">
         <v>6</v>
@@ -6625,15 +6670,15 @@
         <v>45444</v>
       </c>
     </row>
-    <row r="116" spans="1:17">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B116">
         <v>2024</v>
       </c>
       <c r="C116" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D116">
         <v>7</v>
@@ -6678,15 +6723,15 @@
         <v>45474</v>
       </c>
     </row>
-    <row r="117" spans="1:17">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B117">
         <v>2024</v>
       </c>
       <c r="C117" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D117">
         <v>8</v>
@@ -6719,7 +6764,7 @@
         <v>25366.06</v>
       </c>
       <c r="N117">
-        <v>18.17</v>
+        <v>18.170000000000002</v>
       </c>
       <c r="O117">
         <v>17.55</v>
@@ -6731,15 +6776,15 @@
         <v>45505</v>
       </c>
     </row>
-    <row r="118" spans="1:17">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B118">
         <v>2024</v>
       </c>
       <c r="C118" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D118">
         <v>9</v>
@@ -6772,7 +6817,7 @@
         <v>25366.06</v>
       </c>
       <c r="N118">
-        <v>19.67</v>
+        <v>19.670000000000002</v>
       </c>
       <c r="O118">
         <v>16.62</v>
@@ -6784,15 +6829,15 @@
         <v>45536</v>
       </c>
     </row>
-    <row r="119" spans="1:17">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B119">
         <v>2024</v>
       </c>
       <c r="C119" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D119">
         <v>10</v>
@@ -6828,7 +6873,7 @@
         <v>21.15</v>
       </c>
       <c r="O119">
-        <v>16.69</v>
+        <v>16.690000000000001</v>
       </c>
       <c r="P119">
         <v>3.62</v>
@@ -6837,15 +6882,15 @@
         <v>45566</v>
       </c>
     </row>
-    <row r="120" spans="1:17">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B120">
         <v>2024</v>
       </c>
       <c r="C120" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D120">
         <v>11</v>
@@ -6881,7 +6926,7 @@
         <v>22.38</v>
       </c>
       <c r="O120">
-        <v>19.99</v>
+        <v>19.989999999999998</v>
       </c>
       <c r="P120">
         <v>3.62</v>
@@ -6890,15 +6935,15 @@
         <v>45597</v>
       </c>
     </row>
-    <row r="121" spans="1:17">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B121">
         <v>2024</v>
       </c>
       <c r="C121" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D121">
         <v>12</v>
@@ -6934,7 +6979,7 @@
         <v>24.23</v>
       </c>
       <c r="O121">
-        <v>20.26</v>
+        <v>20.260000000000002</v>
       </c>
       <c r="P121">
         <v>3.62</v>
@@ -6943,15 +6988,15 @@
         <v>45627</v>
       </c>
     </row>
-    <row r="122" spans="1:17">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B122">
         <v>2025</v>
       </c>
       <c r="C122" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D122">
         <v>1</v>
@@ -6972,13 +7017,13 @@
         <v>105191.85</v>
       </c>
       <c r="J122">
-        <v>9497.450000000001</v>
+        <v>9497.4500000000007</v>
       </c>
       <c r="K122">
         <v>0</v>
       </c>
       <c r="L122">
-        <v>9497.450000000001</v>
+        <v>9497.4500000000007</v>
       </c>
       <c r="M122">
         <v>25672.68</v>
@@ -6996,15 +7041,15 @@
         <v>45658</v>
       </c>
     </row>
-    <row r="123" spans="1:17">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B123">
         <v>2025</v>
       </c>
       <c r="C123" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D123">
         <v>2</v>
@@ -7025,13 +7070,13 @@
         <v>105191.85</v>
       </c>
       <c r="J123">
-        <v>9497.450000000001</v>
+        <v>9497.4500000000007</v>
       </c>
       <c r="K123">
         <v>0</v>
       </c>
       <c r="L123">
-        <v>9497.450000000001</v>
+        <v>9497.4500000000007</v>
       </c>
       <c r="M123">
         <v>25672.68</v>
@@ -7040,7 +7085,7 @@
         <v>20.32</v>
       </c>
       <c r="O123">
-        <v>17.31</v>
+        <v>17.309999999999999</v>
       </c>
       <c r="P123">
         <v>4.53</v>
@@ -7049,15 +7094,15 @@
         <v>45689</v>
       </c>
     </row>
-    <row r="124" spans="1:17">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B124">
         <v>2025</v>
       </c>
       <c r="C124" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D124">
         <v>3</v>
@@ -7078,13 +7123,13 @@
         <v>105191.85</v>
       </c>
       <c r="J124">
-        <v>9497.450000000001</v>
+        <v>9497.4500000000007</v>
       </c>
       <c r="K124">
         <v>0</v>
       </c>
       <c r="L124">
-        <v>9497.450000000001</v>
+        <v>9497.4500000000007</v>
       </c>
       <c r="M124">
         <v>25672.68</v>
@@ -7102,15 +7147,15 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="125" spans="1:17">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B125">
         <v>2025</v>
       </c>
       <c r="C125" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D125">
         <v>4</v>
@@ -7155,15 +7200,15 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="126" spans="1:17">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B126">
         <v>2025</v>
       </c>
       <c r="C126" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D126">
         <v>5</v>
@@ -7208,15 +7253,15 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="127" spans="1:17">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B127">
         <v>2025</v>
       </c>
       <c r="C127" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D127">
         <v>6</v>
@@ -7261,15 +7306,15 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="128" spans="1:17">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B128">
         <v>2025</v>
       </c>
       <c r="C128" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D128">
         <v>7</v>
@@ -7305,7 +7350,7 @@
         <v>12.59333333333333</v>
       </c>
       <c r="O128">
-        <v>9.640000000000001</v>
+        <v>9.64</v>
       </c>
       <c r="P128">
         <v>4.21</v>
@@ -7314,15 +7359,15 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="129" spans="1:17">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B129">
         <v>2025</v>
       </c>
       <c r="C129" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D129">
         <v>8</v>
@@ -7367,15 +7412,15 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="130" spans="1:17">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B130">
         <v>2025</v>
       </c>
       <c r="C130" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D130">
         <v>9</v>
@@ -7420,15 +7465,15 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="131" spans="1:17">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B131">
         <v>2025</v>
       </c>
       <c r="C131" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D131">
         <v>10</v>
@@ -7461,7 +7506,7 @@
         <v>25672.68</v>
       </c>
       <c r="N131">
-        <v>17.76</v>
+        <v>17.760000000000002</v>
       </c>
       <c r="O131">
         <v>13.87</v>
@@ -7473,15 +7518,15 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="132" spans="1:17">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B132">
         <v>2025</v>
       </c>
       <c r="C132" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D132">
         <v>11</v>
@@ -7517,7 +7562,7 @@
         <v>20.7</v>
       </c>
       <c r="O132">
-        <v>17.17</v>
+        <v>17.170000000000002</v>
       </c>
       <c r="P132">
         <v>3.43</v>
@@ -7526,15 +7571,15 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="133" spans="1:17">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B133">
         <v>2025</v>
       </c>
       <c r="C133" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D133">
         <v>12</v>
@@ -7579,17 +7624,360 @@
         <v>45992</v>
       </c>
     </row>
+    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>16</v>
+      </c>
+      <c r="B134">
+        <v>2026</v>
+      </c>
+      <c r="C134" t="s">
+        <v>17</v>
+      </c>
+      <c r="D134">
+        <v>1</v>
+      </c>
+      <c r="E134">
+        <v>1</v>
+      </c>
+      <c r="F134">
+        <v>41438.75</v>
+      </c>
+      <c r="G134">
+        <v>0</v>
+      </c>
+      <c r="H134">
+        <f>SUM(F134,G134)</f>
+        <v>41438.75</v>
+      </c>
+      <c r="I134">
+        <f>SUM(H134,H137)</f>
+        <v>68336.42</v>
+      </c>
+      <c r="J134">
+        <v>9111.4699999999993</v>
+      </c>
+      <c r="K134">
+        <v>0</v>
+      </c>
+      <c r="L134" s="3">
+        <f>SUM(J134,K134)</f>
+        <v>9111.4699999999993</v>
+      </c>
+      <c r="M134" s="3">
+        <f>SUM(L134,L137)</f>
+        <v>15125.47</v>
+      </c>
+      <c r="N134">
+        <v>23.01</v>
+      </c>
+      <c r="O134">
+        <v>20.21</v>
+      </c>
+      <c r="P134">
+        <v>4.55</v>
+      </c>
+      <c r="Q134" s="2">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>16</v>
+      </c>
+      <c r="B135">
+        <v>2026</v>
+      </c>
+      <c r="C135" t="s">
+        <v>18</v>
+      </c>
+      <c r="D135">
+        <v>2</v>
+      </c>
+      <c r="E135">
+        <v>1</v>
+      </c>
+      <c r="F135">
+        <v>41438.75</v>
+      </c>
+      <c r="G135">
+        <v>0</v>
+      </c>
+      <c r="H135">
+        <f t="shared" ref="H135:H139" si="0">SUM(F135,G135)</f>
+        <v>41438.75</v>
+      </c>
+      <c r="I135">
+        <f t="shared" ref="I135:I136" si="1">SUM(H135,H138)</f>
+        <v>68336.42</v>
+      </c>
+      <c r="J135">
+        <v>9111.4699999999993</v>
+      </c>
+      <c r="K135">
+        <v>0</v>
+      </c>
+      <c r="L135" s="3">
+        <f t="shared" ref="L135:L139" si="2">SUM(J135,K135)</f>
+        <v>9111.4699999999993</v>
+      </c>
+      <c r="M135" s="3">
+        <f t="shared" ref="M135:M136" si="3">SUM(L135,L138)</f>
+        <v>15125.47</v>
+      </c>
+      <c r="N135">
+        <v>28.06</v>
+      </c>
+      <c r="O135">
+        <v>25.79</v>
+      </c>
+      <c r="P135">
+        <v>4.55</v>
+      </c>
+      <c r="Q135" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>16</v>
+      </c>
+      <c r="B136">
+        <v>2026</v>
+      </c>
+      <c r="C136" t="s">
+        <v>19</v>
+      </c>
+      <c r="D136">
+        <v>3</v>
+      </c>
+      <c r="E136">
+        <v>1</v>
+      </c>
+      <c r="F136">
+        <v>41438.75</v>
+      </c>
+      <c r="G136">
+        <v>0</v>
+      </c>
+      <c r="H136">
+        <f t="shared" si="0"/>
+        <v>41438.75</v>
+      </c>
+      <c r="I136">
+        <f t="shared" si="1"/>
+        <v>68336.42</v>
+      </c>
+      <c r="J136">
+        <v>9111.4699999999993</v>
+      </c>
+      <c r="K136">
+        <v>0</v>
+      </c>
+      <c r="L136" s="3">
+        <f t="shared" si="2"/>
+        <v>9111.4699999999993</v>
+      </c>
+      <c r="M136" s="3">
+        <f t="shared" si="3"/>
+        <v>15125.47</v>
+      </c>
+      <c r="N136">
+        <v>24.54</v>
+      </c>
+      <c r="O136">
+        <v>21.12</v>
+      </c>
+      <c r="P136">
+        <v>4.55</v>
+      </c>
+      <c r="Q136" s="2">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>16</v>
+      </c>
+      <c r="B137">
+        <v>2026</v>
+      </c>
+      <c r="C137" t="s">
+        <v>20</v>
+      </c>
+      <c r="D137">
+        <v>4</v>
+      </c>
+      <c r="E137">
+        <v>2</v>
+      </c>
+      <c r="F137">
+        <v>26897.67</v>
+      </c>
+      <c r="G137">
+        <v>0</v>
+      </c>
+      <c r="H137">
+        <f t="shared" si="0"/>
+        <v>26897.67</v>
+      </c>
+      <c r="I137">
+        <f>SUM(H134,H137)</f>
+        <v>68336.42</v>
+      </c>
+      <c r="J137" s="3">
+        <v>6014</v>
+      </c>
+      <c r="K137">
+        <v>0</v>
+      </c>
+      <c r="L137" s="3">
+        <f t="shared" si="2"/>
+        <v>6014</v>
+      </c>
+      <c r="M137" s="3">
+        <f>SUM(L134,L137)</f>
+        <v>15125.47</v>
+      </c>
+      <c r="N137" s="3">
+        <v>24.9</v>
+      </c>
+      <c r="O137" s="3">
+        <v>21.6</v>
+      </c>
+      <c r="P137" s="3">
+        <v>4.47</v>
+      </c>
+      <c r="Q137" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>16</v>
+      </c>
+      <c r="B138">
+        <v>2026</v>
+      </c>
+      <c r="C138" t="s">
+        <v>21</v>
+      </c>
+      <c r="D138">
+        <v>5</v>
+      </c>
+      <c r="E138">
+        <v>2</v>
+      </c>
+      <c r="F138">
+        <v>26897.67</v>
+      </c>
+      <c r="G138">
+        <v>0</v>
+      </c>
+      <c r="H138">
+        <f t="shared" si="0"/>
+        <v>26897.67</v>
+      </c>
+      <c r="I138">
+        <f t="shared" ref="I138:I139" si="4">SUM(H135,H138)</f>
+        <v>68336.42</v>
+      </c>
+      <c r="J138" s="3">
+        <v>6014</v>
+      </c>
+      <c r="K138">
+        <v>0</v>
+      </c>
+      <c r="L138" s="3">
+        <f t="shared" si="2"/>
+        <v>6014</v>
+      </c>
+      <c r="M138" s="3">
+        <f t="shared" ref="M138:M139" si="5">SUM(L135,L138)</f>
+        <v>15125.47</v>
+      </c>
+      <c r="N138" s="3">
+        <v>18.8</v>
+      </c>
+      <c r="O138" s="3">
+        <v>16.170000000000002</v>
+      </c>
+      <c r="P138" s="3">
+        <v>4.47</v>
+      </c>
+      <c r="Q138" s="2">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>16</v>
+      </c>
+      <c r="B139">
+        <v>2026</v>
+      </c>
+      <c r="C139" t="s">
+        <v>22</v>
+      </c>
+      <c r="D139">
+        <v>6</v>
+      </c>
+      <c r="E139">
+        <v>2</v>
+      </c>
+      <c r="F139">
+        <v>26897.67</v>
+      </c>
+      <c r="G139">
+        <v>0</v>
+      </c>
+      <c r="H139">
+        <f t="shared" si="0"/>
+        <v>26897.67</v>
+      </c>
+      <c r="I139">
+        <f t="shared" si="4"/>
+        <v>68336.42</v>
+      </c>
+      <c r="J139" s="3">
+        <v>6014</v>
+      </c>
+      <c r="K139">
+        <v>0</v>
+      </c>
+      <c r="L139" s="3">
+        <f t="shared" si="2"/>
+        <v>6014</v>
+      </c>
+      <c r="M139" s="3">
+        <f t="shared" si="5"/>
+        <v>15125.47</v>
+      </c>
+      <c r="N139" s="3">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="O139" s="3">
+        <v>17.41</v>
+      </c>
+      <c r="P139" s="3">
+        <v>4.47</v>
+      </c>
+      <c r="Q139" s="2">
+        <v>46174</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7597,21 +7985,21 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B2">
         <v>2015</v>
@@ -7629,9 +8017,9 @@
         <v>42339</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B3">
         <v>2018</v>
@@ -7649,9 +8037,9 @@
         <v>43435</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4">
         <v>2021</v>
@@ -7669,9 +8057,9 @@
         <v>44531</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5">
         <v>2023</v>
@@ -7695,62 +8083,65 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G85"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="6" width="18" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2019</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C2">
-        <v>4907.64</v>
+        <v>4907.6400000000003</v>
       </c>
       <c r="D2">
         <v>5140.33</v>
       </c>
       <c r="E2">
-        <v>10047.97</v>
+        <v>10047.969999999999</v>
       </c>
       <c r="F2">
-        <v>4.73</v>
+        <v>4.7300000000000004</v>
       </c>
       <c r="G2" s="2">
         <v>43800</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2019</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C3">
         <v>2713.88</v>
@@ -7768,12 +8159,12 @@
         <v>43800</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2019</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C4">
         <v>7065.63</v>
@@ -7785,18 +8176,18 @@
         <v>13108.02</v>
       </c>
       <c r="F4">
-        <v>4.81</v>
+        <v>4.8099999999999996</v>
       </c>
       <c r="G4" s="2">
         <v>43800</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2019</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C5">
         <v>4878.66</v>
@@ -7814,12 +8205,12 @@
         <v>43800</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2019</v>
       </c>
       <c r="B6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C6">
         <v>13481.88</v>
@@ -7831,18 +8222,18 @@
         <v>25854.41</v>
       </c>
       <c r="F6">
-        <v>5.02</v>
+        <v>5.0199999999999996</v>
       </c>
       <c r="G6" s="2">
         <v>43800</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2019</v>
       </c>
       <c r="B7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C7">
         <v>13773.19</v>
@@ -7860,12 +8251,12 @@
         <v>43800</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2019</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C8">
         <v>2638.13</v>
@@ -7883,12 +8274,12 @@
         <v>43800</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2019</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9">
         <v>3705.73</v>
@@ -7900,18 +8291,18 @@
         <v>7166.77</v>
       </c>
       <c r="F9">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="G9" s="2">
         <v>43800</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2019</v>
       </c>
       <c r="B10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C10">
         <v>1275.78</v>
@@ -7929,21 +8320,21 @@
         <v>43800</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2019</v>
       </c>
       <c r="B11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11">
         <v>4856.54</v>
       </c>
       <c r="D11">
-        <v>4285.4</v>
+        <v>4285.3999999999996</v>
       </c>
       <c r="E11">
-        <v>9141.940000000001</v>
+        <v>9141.94</v>
       </c>
       <c r="F11">
         <v>5.2</v>
@@ -7952,12 +8343,12 @@
         <v>43800</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2019</v>
       </c>
       <c r="B12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C12">
         <v>7366.2</v>
@@ -7975,12 +8366,12 @@
         <v>43800</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2019</v>
       </c>
       <c r="B13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C13">
         <v>5049.45</v>
@@ -7998,12 +8389,12 @@
         <v>43800</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2020</v>
       </c>
       <c r="B14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C14">
         <v>11615.8</v>
@@ -8021,12 +8412,12 @@
         <v>44166</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2020</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C15">
         <v>3058.06</v>
@@ -8035,7 +8426,7 @@
         <v>1513.46</v>
       </c>
       <c r="E15">
-        <v>4571.52</v>
+        <v>4571.5200000000004</v>
       </c>
       <c r="F15">
         <v>3.82</v>
@@ -8044,12 +8435,12 @@
         <v>44166</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2020</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C16">
         <v>6507.32</v>
@@ -8061,18 +8452,18 @@
         <v>12353.53</v>
       </c>
       <c r="F16">
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="G16" s="2">
         <v>44166</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2020</v>
       </c>
       <c r="B17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C17">
         <v>6092.43</v>
@@ -8081,21 +8472,21 @@
         <v>3878.85</v>
       </c>
       <c r="E17">
-        <v>9971.280000000001</v>
+        <v>9971.2800000000007</v>
       </c>
       <c r="F17">
-        <v>4.39</v>
+        <v>4.3899999999999997</v>
       </c>
       <c r="G17" s="2">
         <v>44166</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2020</v>
       </c>
       <c r="B18" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C18">
         <v>13086.45</v>
@@ -8107,18 +8498,18 @@
         <v>21651.95</v>
       </c>
       <c r="F18">
-        <v>4.73</v>
+        <v>4.7300000000000004</v>
       </c>
       <c r="G18" s="2">
         <v>44166</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2020</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C19">
         <v>2346.39</v>
@@ -8136,12 +8527,12 @@
         <v>44166</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2020</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C20">
         <v>3798.72</v>
@@ -8159,12 +8550,12 @@
         <v>44166</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2020</v>
       </c>
       <c r="B21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C21">
         <v>1375.93</v>
@@ -8182,35 +8573,35 @@
         <v>44166</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2020</v>
       </c>
       <c r="B22" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C22">
-        <v>4809.9</v>
+        <v>4809.8999999999996</v>
       </c>
       <c r="D22">
-        <v>4562.94</v>
+        <v>4562.9399999999996</v>
       </c>
       <c r="E22">
         <v>9372.84</v>
       </c>
       <c r="F22">
-        <v>4.85</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="G22" s="2">
         <v>44166</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2020</v>
       </c>
       <c r="B23" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C23">
         <v>7153.05</v>
@@ -8228,12 +8619,12 @@
         <v>44166</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2020</v>
       </c>
       <c r="B24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C24">
         <v>5037.21</v>
@@ -8251,12 +8642,12 @@
         <v>44166</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2020</v>
       </c>
       <c r="B25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C25">
         <v>5568.89</v>
@@ -8274,12 +8665,12 @@
         <v>44166</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2021</v>
       </c>
       <c r="B26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C26">
         <v>2770.18</v>
@@ -8297,12 +8688,12 @@
         <v>44531</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2021</v>
       </c>
       <c r="B27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C27">
         <v>4592.68</v>
@@ -8311,21 +8702,21 @@
         <v>4559.2</v>
       </c>
       <c r="E27">
-        <v>9151.879999999999</v>
+        <v>9151.8799999999992</v>
       </c>
       <c r="F27">
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="G27" s="2">
         <v>44531</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2021</v>
       </c>
       <c r="B28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C28">
         <v>5907.3</v>
@@ -8334,7 +8725,7 @@
         <v>3146</v>
       </c>
       <c r="E28">
-        <v>9053.299999999999</v>
+        <v>9053.2999999999993</v>
       </c>
       <c r="F28">
         <v>4.2</v>
@@ -8343,12 +8734,12 @@
         <v>44531</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2021</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C29">
         <v>2161.5</v>
@@ -8366,12 +8757,12 @@
         <v>44531</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>2021</v>
       </c>
       <c r="B30" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C30">
         <v>11036.96</v>
@@ -8383,27 +8774,27 @@
         <v>19099.84</v>
       </c>
       <c r="F30">
-        <v>5.11</v>
+        <v>5.1100000000000003</v>
       </c>
       <c r="G30" s="2">
         <v>44531</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>2021</v>
       </c>
       <c r="B31" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C31">
         <v>10007.98</v>
       </c>
       <c r="D31">
-        <v>8885.940000000001</v>
+        <v>8885.94</v>
       </c>
       <c r="E31">
-        <v>18893.92</v>
+        <v>18893.919999999998</v>
       </c>
       <c r="F31">
         <v>3.89</v>
@@ -8412,12 +8803,12 @@
         <v>44531</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>2021</v>
       </c>
       <c r="B32" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C32">
         <v>5999.6</v>
@@ -8426,7 +8817,7 @@
         <v>2323.52</v>
       </c>
       <c r="E32">
-        <v>8323.120000000001</v>
+        <v>8323.1200000000008</v>
       </c>
       <c r="F32">
         <v>4.82</v>
@@ -8435,12 +8826,12 @@
         <v>44531</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>2021</v>
       </c>
       <c r="B33" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C33">
         <v>1399.75</v>
@@ -8458,12 +8849,12 @@
         <v>44531</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>2021</v>
       </c>
       <c r="B34" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C34">
         <v>4793.72</v>
@@ -8472,7 +8863,7 @@
         <v>3482.09</v>
       </c>
       <c r="E34">
-        <v>8275.809999999999</v>
+        <v>8275.81</v>
       </c>
       <c r="F34">
         <v>4.68</v>
@@ -8481,12 +8872,12 @@
         <v>44531</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>2021</v>
       </c>
       <c r="B35" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C35">
         <v>6995.8</v>
@@ -8504,12 +8895,12 @@
         <v>44531</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>2021</v>
       </c>
       <c r="B36" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C36">
         <v>4796.46</v>
@@ -8527,12 +8918,12 @@
         <v>44531</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>2021</v>
       </c>
       <c r="B37" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C37">
         <v>890.51</v>
@@ -8550,12 +8941,12 @@
         <v>44531</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>2022</v>
       </c>
       <c r="B38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C38">
         <v>11610.99</v>
@@ -8573,12 +8964,12 @@
         <v>44896</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>2022</v>
       </c>
       <c r="B39" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C39">
         <v>2709.32</v>
@@ -8587,7 +8978,7 @@
         <v>1701.45</v>
       </c>
       <c r="E39">
-        <v>4410.77</v>
+        <v>4410.7700000000004</v>
       </c>
       <c r="F39">
         <v>4.34</v>
@@ -8596,35 +8987,35 @@
         <v>44896</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>2022</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C40">
-        <v>4459.02</v>
+        <v>4459.0200000000004</v>
       </c>
       <c r="D40">
         <v>3893.67</v>
       </c>
       <c r="E40">
-        <v>8352.690000000001</v>
+        <v>8352.69</v>
       </c>
       <c r="F40">
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="G40" s="2">
         <v>44896</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>2022</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C41">
         <v>4827.22</v>
@@ -8642,38 +9033,38 @@
         <v>44896</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>2022</v>
       </c>
       <c r="B42" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C42">
         <v>2017.29</v>
       </c>
       <c r="D42">
-        <v>2168.95</v>
+        <v>2168.9499999999998</v>
       </c>
       <c r="E42">
         <v>4186.24</v>
       </c>
       <c r="F42">
-        <v>5.02</v>
+        <v>5.0199999999999996</v>
       </c>
       <c r="G42" s="2">
         <v>44896</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>2022</v>
       </c>
       <c r="B43" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C43">
-        <v>8956.440000000001</v>
+        <v>8956.44</v>
       </c>
       <c r="D43">
         <v>8290.43</v>
@@ -8682,18 +9073,18 @@
         <v>17246.87</v>
       </c>
       <c r="F43">
-        <v>4.52</v>
+        <v>4.5199999999999996</v>
       </c>
       <c r="G43" s="2">
         <v>44896</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>2022</v>
       </c>
       <c r="B44" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C44">
         <v>5250.59</v>
@@ -8711,12 +9102,12 @@
         <v>44896</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>2022</v>
       </c>
       <c r="B45" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C45">
         <v>1033.8</v>
@@ -8728,21 +9119,21 @@
         <v>1806.45</v>
       </c>
       <c r="F45">
-        <v>4.44</v>
+        <v>4.4400000000000004</v>
       </c>
       <c r="G45" s="2">
         <v>44896</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>2022</v>
       </c>
       <c r="B46" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C46">
-        <v>1294.41</v>
+        <v>1294.4100000000001</v>
       </c>
       <c r="D46">
         <v>1275.3</v>
@@ -8757,12 +9148,12 @@
         <v>44896</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>2022</v>
       </c>
       <c r="B47" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C47">
         <v>3563.46</v>
@@ -8774,18 +9165,18 @@
         <v>7372.88</v>
       </c>
       <c r="F47">
-        <v>4.64</v>
+        <v>4.6399999999999997</v>
       </c>
       <c r="G47" s="2">
         <v>44896</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>2022</v>
       </c>
       <c r="B48" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C48">
         <v>7323</v>
@@ -8803,12 +9194,12 @@
         <v>44896</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>2022</v>
       </c>
       <c r="B49" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C49">
         <v>5006.25</v>
@@ -8826,12 +9217,12 @@
         <v>44896</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>2023</v>
       </c>
       <c r="B50" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C50">
         <v>2694.26</v>
@@ -8849,12 +9240,12 @@
         <v>45261</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>2023</v>
       </c>
       <c r="B51" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C51">
         <v>3821.71</v>
@@ -8866,18 +9257,18 @@
         <v>7504.35</v>
       </c>
       <c r="F51">
-        <v>4.61</v>
+        <v>4.6100000000000003</v>
       </c>
       <c r="G51" s="2">
         <v>45261</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>2023</v>
       </c>
       <c r="B52" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C52">
         <v>3957.84</v>
@@ -8895,18 +9286,18 @@
         <v>45261</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>2023</v>
       </c>
       <c r="B53" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C53">
         <v>2017</v>
       </c>
       <c r="D53">
-        <v>2143.78</v>
+        <v>2143.7800000000002</v>
       </c>
       <c r="E53">
         <v>4160.78</v>
@@ -8918,12 +9309,12 @@
         <v>45261</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>2023</v>
       </c>
       <c r="B54" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C54">
         <v>10776.49</v>
@@ -8935,18 +9326,18 @@
         <v>18293.96</v>
       </c>
       <c r="F54">
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="G54" s="2">
         <v>45261</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>2023</v>
       </c>
       <c r="B55" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C55">
         <v>11617.73</v>
@@ -8964,12 +9355,12 @@
         <v>45261</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>2023</v>
       </c>
       <c r="B56" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C56">
         <v>653.4</v>
@@ -8981,18 +9372,18 @@
         <v>1202.8</v>
       </c>
       <c r="F56">
-        <v>4.15</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="G56" s="2">
         <v>45261</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>2023</v>
       </c>
       <c r="B57" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C57">
         <v>1225.31</v>
@@ -9001,7 +9392,7 @@
         <v>1136.43</v>
       </c>
       <c r="E57">
-        <v>2361.74</v>
+        <v>2361.7399999999998</v>
       </c>
       <c r="F57">
         <v>3.98</v>
@@ -9010,12 +9401,12 @@
         <v>45261</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>2023</v>
       </c>
       <c r="B58" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C58">
         <v>3821.06</v>
@@ -9033,12 +9424,12 @@
         <v>45261</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>2023</v>
       </c>
       <c r="B59" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C59">
         <v>6973.15</v>
@@ -9056,12 +9447,12 @@
         <v>45261</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>2023</v>
       </c>
       <c r="B60" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C60">
         <v>4978.95</v>
@@ -9070,21 +9461,21 @@
         <v>3891</v>
       </c>
       <c r="E60">
-        <v>8869.950000000001</v>
+        <v>8869.9500000000007</v>
       </c>
       <c r="F60">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="G60" s="2">
         <v>45261</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>2023</v>
       </c>
       <c r="B61" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C61">
         <v>5119.41</v>
@@ -9096,18 +9487,18 @@
         <v>8155</v>
       </c>
       <c r="F61">
-        <v>4.27</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="G61" s="2">
         <v>45261</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>2024</v>
       </c>
       <c r="B62" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C62">
         <v>10511.38</v>
@@ -9125,12 +9516,12 @@
         <v>45627</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>2024</v>
       </c>
       <c r="B63" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C63">
         <v>2143.12</v>
@@ -9148,12 +9539,12 @@
         <v>45627</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>2024</v>
       </c>
       <c r="B64" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C64">
         <v>3859.07</v>
@@ -9165,18 +9556,18 @@
         <v>7285.37</v>
       </c>
       <c r="F64">
-        <v>4.61</v>
+        <v>4.6100000000000003</v>
       </c>
       <c r="G64" s="2">
         <v>45627</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>2024</v>
       </c>
       <c r="B65" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C65">
         <v>4703.47</v>
@@ -9194,12 +9585,12 @@
         <v>45627</v>
       </c>
     </row>
-    <row r="66" spans="1:7">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>2024</v>
       </c>
       <c r="B66" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C66">
         <v>1676.51</v>
@@ -9217,12 +9608,12 @@
         <v>45627</v>
       </c>
     </row>
-    <row r="67" spans="1:7">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>2024</v>
       </c>
       <c r="B67" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C67">
         <v>7170.8</v>
@@ -9240,18 +9631,18 @@
         <v>45627</v>
       </c>
     </row>
-    <row r="68" spans="1:7">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>2024</v>
       </c>
       <c r="B68" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C68">
         <v>948.9</v>
       </c>
       <c r="D68">
-        <v>1072.64</v>
+        <v>1072.6400000000001</v>
       </c>
       <c r="E68">
         <v>2021.54</v>
@@ -9263,12 +9654,12 @@
         <v>45627</v>
       </c>
     </row>
-    <row r="69" spans="1:7">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>2024</v>
       </c>
       <c r="B69" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C69">
         <v>475.6</v>
@@ -9286,12 +9677,12 @@
         <v>45627</v>
       </c>
     </row>
-    <row r="70" spans="1:7">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>2024</v>
       </c>
       <c r="B70" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C70">
         <v>3755.93</v>
@@ -9309,12 +9700,12 @@
         <v>45627</v>
       </c>
     </row>
-    <row r="71" spans="1:7">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>2024</v>
       </c>
       <c r="B71" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C71">
         <v>6221.85</v>
@@ -9323,24 +9714,24 @@
         <v>3052.2</v>
       </c>
       <c r="E71">
-        <v>9274.049999999999</v>
+        <v>9274.0499999999993</v>
       </c>
       <c r="F71">
-        <v>4.36</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="G71" s="2">
         <v>45627</v>
       </c>
     </row>
-    <row r="72" spans="1:7">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>2024</v>
       </c>
       <c r="B72" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C72">
-        <v>4493.1</v>
+        <v>4493.1000000000004</v>
       </c>
       <c r="D72">
         <v>3191.5</v>
@@ -9355,12 +9746,12 @@
         <v>45627</v>
       </c>
     </row>
-    <row r="73" spans="1:7">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>2024</v>
       </c>
       <c r="B73" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C73">
         <v>3899.85</v>
@@ -9378,15 +9769,15 @@
         <v>45627</v>
       </c>
     </row>
-    <row r="74" spans="1:7">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>2025</v>
       </c>
       <c r="B74" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C74">
-        <v>4130.73</v>
+        <v>4130.7299999999996</v>
       </c>
       <c r="D74">
         <v>2978.9</v>
@@ -9401,12 +9792,12 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="75" spans="1:7">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>2025</v>
       </c>
       <c r="B75" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C75">
         <v>1659.94</v>
@@ -9418,21 +9809,21 @@
         <v>3423.11</v>
       </c>
       <c r="F75">
-        <v>4.64</v>
+        <v>4.6399999999999997</v>
       </c>
       <c r="G75" s="2">
         <v>45992</v>
       </c>
     </row>
-    <row r="76" spans="1:7">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>2025</v>
       </c>
       <c r="B76" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C76">
-        <v>9505.790000000001</v>
+        <v>9505.7900000000009</v>
       </c>
       <c r="D76">
         <v>6823.46</v>
@@ -9441,24 +9832,24 @@
         <v>16329.25</v>
       </c>
       <c r="F76">
-        <v>5.06</v>
+        <v>5.0599999999999996</v>
       </c>
       <c r="G76" s="2">
         <v>45992</v>
       </c>
     </row>
-    <row r="77" spans="1:7">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>2025</v>
       </c>
       <c r="B77" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C77">
         <v>8965.92</v>
       </c>
       <c r="D77">
-        <v>9545.450000000001</v>
+        <v>9545.4500000000007</v>
       </c>
       <c r="E77">
         <v>18511.37</v>
@@ -9470,12 +9861,12 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="78" spans="1:7">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>2025</v>
       </c>
       <c r="B78" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C78">
         <v>3376.48</v>
@@ -9493,12 +9884,12 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="79" spans="1:7">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>2025</v>
       </c>
       <c r="B79" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C79">
         <v>721.1</v>
@@ -9516,12 +9907,12 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="80" spans="1:7">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>2025</v>
       </c>
       <c r="B80" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C80">
         <v>3483.63</v>
@@ -9539,18 +9930,18 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="81" spans="1:7">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>2025</v>
       </c>
       <c r="B81" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C81">
         <v>6792.7</v>
       </c>
       <c r="D81">
-        <v>4952.73</v>
+        <v>4952.7299999999996</v>
       </c>
       <c r="E81">
         <v>11745.43</v>
@@ -9562,12 +9953,12 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="82" spans="1:7">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>2025</v>
       </c>
       <c r="B82" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C82">
         <v>4552.57</v>
@@ -9579,18 +9970,18 @@
         <v>7600.33</v>
       </c>
       <c r="F82">
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="G82" s="2">
         <v>45992</v>
       </c>
     </row>
-    <row r="83" spans="1:7">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>2025</v>
       </c>
       <c r="B83" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C83">
         <v>3771.62</v>
@@ -9608,12 +9999,12 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="84" spans="1:7">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>2025</v>
       </c>
       <c r="B84" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C84">
         <v>530.5</v>
@@ -9631,12 +10022,12 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="85" spans="1:7">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>2025</v>
       </c>
       <c r="B85" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C85">
         <v>2027.51</v>
@@ -9648,7 +10039,7 @@
         <v>2486.13</v>
       </c>
       <c r="F85">
-        <v>4.27</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="G85" s="2">
         <v>45992</v>
